--- a/docs/reports/UEC.xlsx
+++ b/docs/reports/UEC.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,20 +160,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +179,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -563,14 +560,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UEC (UEC)</t>
+          <t>Uranium Energy Corp. (UEC)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · High-growth (2-Stage FCFE) · generated 2026-07-08 · data: yfinance</t>
+          <t>Energy · Cyclical / Commodities (mid-cycle multiples + DCF) · generated 2026-10-13 · data: Yahoo snapshot as of 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -588,7 +585,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -610,11 +607,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v/>
+        <v>3.972000122070312</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +699,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -744,16 +741,16 @@
           <t>Ordinary Shares Number</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>289.638307</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>378.452864</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>410.355768</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>454.015855</v>
       </c>
     </row>
@@ -763,16 +760,16 @@
           <t>Share Issued</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>289.638307</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>378.452864</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>410.355768</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>454.015855</v>
       </c>
     </row>
@@ -782,7 +779,7 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>10.075</v>
       </c>
     </row>
@@ -792,16 +789,16 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -811,16 +808,16 @@
           <t>Invested Capital</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -830,16 +827,16 @@
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>93.693</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>43.011</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>206.022</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>207.583</v>
       </c>
     </row>
@@ -849,16 +846,16 @@
           <t>Net Tangible Assets</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -868,16 +865,16 @@
           <t>Common Stock Equity</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -887,16 +884,16 @@
           <t>Total Capitalization</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -906,16 +903,16 @@
           <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -925,16 +922,16 @@
           <t>Stockholders Equity</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>326.909</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>631.827</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>778.1130000000001</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>983.9</v>
       </c>
     </row>
@@ -944,7 +941,7 @@
           <t>Other Equity Interest</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="25" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -954,16 +951,16 @@
           <t>Gains Losses Not Affecting Retained Earnings</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>-0.186</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>-3.608</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>-13.829</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>-14.417</v>
       </c>
     </row>
@@ -973,16 +970,16 @@
           <t>Other Equity Adjustments</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-0.186</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>-3.608</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>-13.829</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>-14.417</v>
       </c>
     </row>
@@ -992,16 +989,16 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-286.373</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-289.68</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>-318.901</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>-406.557</v>
       </c>
     </row>
@@ -1011,16 +1008,16 @@
           <t>Additional Paid In Capital</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>613.179</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>924.737</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>1110.433</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>1404.42</v>
       </c>
     </row>
@@ -1030,16 +1027,16 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>0.289</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>0.378</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>0.41</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>0.454</v>
       </c>
     </row>
@@ -1049,16 +1046,16 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>0.289</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>0.378</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>0.41</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>0.454</v>
       </c>
     </row>
@@ -1068,16 +1065,16 @@
           <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>27.338</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>105.762</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>111.715</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>123.753</v>
       </c>
     </row>
@@ -1087,16 +1084,16 @@
           <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>18.84</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>93.568</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>82.49299999999999</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>97.31999999999999</v>
       </c>
     </row>
@@ -1106,16 +1103,16 @@
           <t>Other Non Current Liabilities</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>1.028</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>1.02</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>1.474</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>1.293</v>
       </c>
     </row>
@@ -1125,13 +1122,13 @@
           <t>Derivative Product Liabilities</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>4.313</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1141,16 +1138,16 @@
           <t>Non Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>0.536</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>71.08</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>64.34699999999999</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>62.123</v>
       </c>
     </row>
@@ -1160,16 +1157,16 @@
           <t>Non Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>0.536</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>71.08</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>64.34699999999999</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>62.123</v>
       </c>
     </row>
@@ -1179,7 +1176,7 @@
           <t>Long Term Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="25" t="n">
         <v>0.065952</v>
       </c>
     </row>
@@ -1189,7 +1186,7 @@
           <t>Long Term Debt</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="25" t="n">
         <v>0.065952</v>
       </c>
     </row>
@@ -1199,16 +1196,16 @@
           <t>Long Term Provisions</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>17.276</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>17.155</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>16.672</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>33.904</v>
       </c>
     </row>
@@ -1218,16 +1215,16 @@
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>8.497999999999999</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>12.194</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>29.222</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>26.433</v>
       </c>
     </row>
@@ -1237,16 +1234,16 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>0.336</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>0.154</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>3.331</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>0.713</v>
       </c>
     </row>
@@ -1256,7 +1253,7 @@
           <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="25" t="n">
         <v>10.075</v>
       </c>
     </row>
@@ -1266,7 +1263,7 @@
           <t>Current Debt</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <v>10.075</v>
       </c>
     </row>
@@ -1276,7 +1273,7 @@
           <t>Other Current Borrowings</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <v>0.19151</v>
       </c>
     </row>
@@ -1286,10 +1283,10 @@
           <t>Line Of Credit</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="25" t="n">
         <v>10.075</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1299,13 +1296,13 @@
           <t>Current Provisions</t>
         </is>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>1.515</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>2.953</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>5.16</v>
       </c>
     </row>
@@ -1315,16 +1312,16 @@
           <t>Payables And Accrued Expenses</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>8.162000000000001</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>10.525</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>22.938</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>20.56</v>
       </c>
     </row>
@@ -1334,16 +1331,16 @@
           <t>Current Accrued Expenses</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>5.443</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>4.949</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>7.075</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>9.975</v>
       </c>
     </row>
@@ -1353,16 +1350,16 @@
           <t>Payables</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>2.719</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>5.576</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>15.863</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>10.585</v>
       </c>
     </row>
@@ -1372,10 +1369,10 @@
           <t>Other Payable</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>0.704</v>
       </c>
     </row>
@@ -1385,7 +1382,7 @@
           <t>Dueto Related Parties Current</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="25" t="n">
         <v>0.000843</v>
       </c>
     </row>
@@ -1395,16 +1392,16 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>2.019</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>5.576</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>15.863</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>10.585</v>
       </c>
     </row>
@@ -1414,16 +1411,16 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>354.247</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>737.5890000000001</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>889.828</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>1107.653</v>
       </c>
     </row>
@@ -1433,16 +1430,16 @@
           <t>Total Non Current Assets</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>252.056</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>682.384</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>654.5839999999999</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>873.6369999999999</v>
       </c>
     </row>
@@ -1452,16 +1449,16 @@
           <t>Other Non Current Assets</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>10.863</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>10.33</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>11.194</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>12.178</v>
       </c>
     </row>
@@ -1471,16 +1468,16 @@
           <t>Investments And Advances</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>39.011</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>86.76600000000001</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>65.342</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>84.295</v>
       </c>
     </row>
@@ -1490,16 +1487,16 @@
           <t>Investmentin Financial Assets</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>14.834</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>38.656</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>6.533</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>28.47</v>
       </c>
     </row>
@@ -1509,16 +1506,16 @@
           <t>Available For Sale Securities</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>14.834</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>38.656</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>6.533</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>28.47</v>
       </c>
     </row>
@@ -1528,16 +1525,16 @@
           <t>Long Term Equity Investment</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>24.177</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>48.11</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>58.809</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>55.825</v>
       </c>
     </row>
@@ -1547,16 +1544,16 @@
           <t>Net PPE</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>202.182</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>585.288</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>578.048</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>777.164</v>
       </c>
     </row>
@@ -1566,16 +1563,16 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>-12.489</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>-13.513</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>-14.527</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>-18.298</v>
       </c>
     </row>
@@ -1585,16 +1582,16 @@
           <t>Gross PPE</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>214.671</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>598.801</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>592.575</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>795.462</v>
       </c>
     </row>
@@ -1604,10 +1601,10 @@
           <t>Other Properties</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="25" t="n">
         <v>1.924</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>2.666</v>
       </c>
     </row>
@@ -1617,16 +1614,16 @@
           <t>Machinery Furniture Equipment</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>22.18</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>22.448</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>23.341</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>67.649</v>
       </c>
     </row>
@@ -1636,16 +1633,16 @@
           <t>Buildings And Improvements</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>0.298</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>0.297</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>0.337</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>2.086</v>
       </c>
     </row>
@@ -1655,16 +1652,16 @@
           <t>Land And Improvements</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>1.08</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>1.08</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>1.08</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>1.514</v>
       </c>
     </row>
@@ -1674,16 +1671,16 @@
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>102.191</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>55.205</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>235.244</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>234.016</v>
       </c>
     </row>
@@ -1693,16 +1690,16 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B60" s="29" t="n">
+      <c r="B60" s="25" t="n">
         <v>0.126</v>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>0.214</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>0.702</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -1712,16 +1709,16 @@
           <t>Prepaid Assets</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n">
+      <c r="B61" s="25" t="n">
         <v>1.434</v>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>2.871</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>2.682</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="25" t="n">
         <v>2.453</v>
       </c>
     </row>
@@ -1731,16 +1728,16 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="25" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="25" t="n">
         <v>6.207</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="25" t="n">
         <v>75.833</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="25" t="n">
         <v>79.279</v>
       </c>
     </row>
@@ -1750,13 +1747,13 @@
           <t>Other Inventories</t>
         </is>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="25" t="n">
         <v>5.801</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="25" t="n">
         <v>75.44</v>
       </c>
-      <c r="F63" s="29" t="n">
+      <c r="F63" s="25" t="n">
         <v>72.899</v>
       </c>
     </row>
@@ -1766,16 +1763,16 @@
           <t>Finished Goods</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="25" t="n">
         <v>66.33799999999999</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="25" t="n">
         <v>0.178</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="25" t="n">
         <v>0.178</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="25" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -1785,10 +1782,10 @@
           <t>Work In Process</t>
         </is>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="29" t="n">
+      <c r="F65" s="25" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -1798,16 +1795,16 @@
           <t>Raw Materials</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="25" t="n">
         <v>0.232</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="25" t="n">
         <v>0.228</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="25" t="n">
         <v>0.215</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="F66" s="25" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1817,16 +1814,16 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="25" t="n">
         <v>2.871</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="25" t="n">
         <v>2.682</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="25" t="n">
         <v>3.147</v>
       </c>
-      <c r="F67" s="29" t="n">
+      <c r="F67" s="25" t="n">
         <v>5.807</v>
       </c>
     </row>
@@ -1836,16 +1833,16 @@
           <t>Other Receivables</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="25" t="n">
         <v>2.871</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="25" t="n">
         <v>2.682</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="25" t="n">
         <v>3.147</v>
       </c>
-      <c r="F68" s="29" t="n">
+      <c r="F68" s="25" t="n">
         <v>5.807</v>
       </c>
     </row>
@@ -1855,16 +1852,16 @@
           <t>Cash Cash Equivalents And Short Term Investments</t>
         </is>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="25" t="n">
         <v>32.536</v>
       </c>
-      <c r="D69" s="29" t="n">
+      <c r="D69" s="25" t="n">
         <v>45.614</v>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="25" t="n">
         <v>156.264</v>
       </c>
-      <c r="F69" s="29" t="n">
+      <c r="F69" s="25" t="n">
         <v>148.93</v>
       </c>
     </row>
@@ -1874,13 +1871,13 @@
           <t>Other Short Term Investments</t>
         </is>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D70" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="25" t="n">
         <v>68.73099999999999</v>
       </c>
-      <c r="F70" s="29" t="n">
+      <c r="F70" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1890,16 +1887,16 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="25" t="n">
         <v>32.536</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="25" t="n">
         <v>45.614</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="25" t="n">
         <v>87.533</v>
       </c>
-      <c r="F71" s="29" t="n">
+      <c r="F71" s="25" t="n">
         <v>148.93</v>
       </c>
     </row>
@@ -1935,7 +1932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -1977,16 +1974,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-54.197</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>71.917</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>-109.915</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>-70.15300000000001</v>
       </c>
     </row>
@@ -1996,10 +1993,10 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="25" t="n">
         <v>-0.833363</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>-0.5570000000000001</v>
       </c>
     </row>
@@ -2009,16 +2006,16 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-10.191</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>-0.066</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2028,10 +2025,10 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2041,16 +2038,16 @@
           <t>Issuance Of Capital Stock</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>168.014</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>66.527</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>176.708</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>287.513</v>
       </c>
     </row>
@@ -2060,16 +2057,16 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>-1.21</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>-0.656</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>-3.428</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>-5.695</v>
       </c>
     </row>
@@ -2079,16 +2076,16 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>39.787</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>52.865</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>94.78400000000001</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>158.137</v>
       </c>
     </row>
@@ -2098,16 +2095,16 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>46.351</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>39.787</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>52.865</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>94.78400000000001</v>
       </c>
     </row>
@@ -2117,16 +2114,16 @@
           <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>-0.132</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>-0.029</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -2136,16 +2133,16 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>-6.564</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>13.21</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>41.948</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>63.352</v>
       </c>
     </row>
@@ -2155,16 +2152,16 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>157.266</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>65.417</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>173.076</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>284.839</v>
       </c>
     </row>
@@ -2174,16 +2171,16 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>157.266</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>65.417</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>173.076</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>284.839</v>
       </c>
     </row>
@@ -2193,16 +2190,16 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>-0.5570000000000001</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>-1.044</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>-3.632</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>-2.674</v>
       </c>
     </row>
@@ -2212,13 +2209,13 @@
           <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="25" t="n">
         <v>-0.833</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-0.5570000000000001</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>-1.044</v>
       </c>
     </row>
@@ -2228,16 +2225,16 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>168.014</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>66.527</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>176.708</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>287.513</v>
       </c>
     </row>
@@ -2247,10 +2244,10 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="25" t="n">
         <v>-0.833363</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-0.5570000000000001</v>
       </c>
     </row>
@@ -2260,16 +2257,16 @@
           <t>Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>168.014</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>66.527</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>176.708</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>287.513</v>
       </c>
     </row>
@@ -2279,16 +2276,16 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>-10.191</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>-0.066</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2298,16 +2295,16 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>-10.191</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>-0.066</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2317,16 +2314,16 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>-10.191</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>-0.066</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2336,10 +2333,10 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2349,16 +2346,16 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>-110.843</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>-124.78</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>-24.641</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>-157.029</v>
       </c>
     </row>
@@ -2368,16 +2365,16 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>-110.843</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>-124.78</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>-24.641</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>-157.029</v>
       </c>
     </row>
@@ -2387,16 +2384,16 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>9.19</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>0.026</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>0.008</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>-179.539</v>
       </c>
     </row>
@@ -2406,16 +2403,16 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>-5.235</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-42.602</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>-9.106999999999999</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>28.743</v>
       </c>
     </row>
@@ -2425,16 +2422,16 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>9.98</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>4.59</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>3.008</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>54.438</v>
       </c>
     </row>
@@ -2444,16 +2441,16 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>-15.215</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>-47.192</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>-12.115</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>-25.695</v>
       </c>
     </row>
@@ -2463,16 +2460,16 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>-113.588</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-81.548</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>-12.114</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>-0.538</v>
       </c>
     </row>
@@ -2482,16 +2479,16 @@
           <t>Sale Of Business</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>1.984</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2501,16 +2498,16 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-113.588</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>-83.532</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>-12.114</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>-0.538</v>
       </c>
     </row>
@@ -2520,16 +2517,16 @@
           <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-1.21</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-0.656</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>-3.428</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>-5.695</v>
       </c>
     </row>
@@ -2539,16 +2536,16 @@
           <t>Purchase Of PPE</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-1.21</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-0.656</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-3.428</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>-5.695</v>
       </c>
     </row>
@@ -2558,16 +2555,16 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>-52.987</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>72.57299999999999</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>-106.487</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>-64.458</v>
       </c>
     </row>
@@ -2577,16 +2574,16 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>-52.987</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>72.57299999999999</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>-106.487</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>-64.458</v>
       </c>
     </row>
@@ -2596,16 +2593,16 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-35.495</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>57.032</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>-59.318</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>-4.319</v>
       </c>
     </row>
@@ -2615,16 +2612,16 @@
           <t>Change In Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>-0.17</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>0.058</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>0.022</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>0.228</v>
       </c>
     </row>
@@ -2634,16 +2631,16 @@
           <t>Change In Other Current Assets</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>0.017</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>0.519</v>
       </c>
     </row>
@@ -2653,16 +2650,16 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>3.262</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>-4.355</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>10.36</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>-2.993</v>
       </c>
     </row>
@@ -2672,7 +2669,7 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="25" t="n">
         <v>0.669126</v>
       </c>
     </row>
@@ -2682,7 +2679,7 @@
           <t>Change In Account Payable</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="25" t="n">
         <v>0.699617</v>
       </c>
     </row>
@@ -2692,16 +2689,16 @@
           <t>Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>-1.398</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>0.966</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>-0.074</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>0.232</v>
       </c>
     </row>
@@ -2711,16 +2708,16 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>-37.206</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>60.363</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>-69.626</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>-2.305</v>
       </c>
     </row>
@@ -2730,13 +2727,13 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="25" t="n">
         <v>1.09</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>-17.817</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>-0.428</v>
       </c>
     </row>
@@ -2746,16 +2743,16 @@
           <t>Stock Based Compensation</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>4.681</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>5.523</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>5.172</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>6.015</v>
       </c>
     </row>
@@ -2765,16 +2762,16 @@
           <t>Unrealized Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>1.351</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>13.083</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>-27.505</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>18.051</v>
       </c>
     </row>
@@ -2784,16 +2781,16 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>0.112</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2803,16 +2800,16 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>0.87</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>-5.034</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>-2.779</v>
       </c>
     </row>
@@ -2822,16 +2819,16 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>0.87</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>-5.034</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>-2.779</v>
       </c>
     </row>
@@ -2841,16 +2838,16 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>4.486</v>
       </c>
     </row>
@@ -2860,16 +2857,16 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>4.486</v>
       </c>
     </row>
@@ -2879,16 +2876,16 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>4.486</v>
       </c>
     </row>
@@ -2898,16 +2895,16 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>-12.333</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>-2.319</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>7.236</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>1.744</v>
       </c>
     </row>
@@ -2917,16 +2914,16 @@
           <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>-4.126</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>0.994</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>-1.017</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>3.352</v>
       </c>
     </row>
@@ -2936,13 +2933,13 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>-3.293</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>8.226000000000001</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>-1.706</v>
       </c>
     </row>
@@ -2952,16 +2949,16 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -2971,6 +2968,272 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UEC — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Mid-cycle normalized EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.6193872776127251</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.4831220765379255</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.7556524786875245</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>excluded — implausible: 0.1x the current price</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/Sales</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2.182910991071005</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1.719190291272978</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2.739375830828639</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Price / Book</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4.550920363783331</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3.413190272837499</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>5.916196472918331</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>SUMPRODUCT(C5:C7,F5:F7)/SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.0936</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>$B$10*(1+$B$11)-$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B14" s="17">
+        <f>$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>9.930000305175781</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3.972000122070312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Mid-cycle normalized EV/EBITDA excluded (0.1x the current price is outside the 0.2x–5x plausibility band).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Target 3.68 fell outside 0.4x–2.5x the price and was limited to the band edge.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2995,14 +3258,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UEC — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+          <t>UEC — projected P&amp;L &amp; levered FCF (DCF base case)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
         </is>
       </c>
     </row>
@@ -3064,40 +3327,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue (mn)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>68.84211000000001</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>70.9073733</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>73.03459449899999</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>75.22563233397</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>77.48240130398909</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>79.80687334310878</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>82.20107954340205</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>84.66711192970412</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>87.20712528759525</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>89.8233390462231</v>
+      <c r="B5" s="18" t="n">
+        <v>83.54625</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>94.31923139066612</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>103.7055152106564</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>111.8379416678953</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>118.9166292665171</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>125.1540410724432</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>130.7458645198486</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>135.8590327290696</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>140.6295043726961</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>144.1452419820135</v>
       </c>
     </row>
     <row r="6">
@@ -3111,39 +3374,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3154,35 +3417,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>-1.098508311264719</v>
+      <c r="B7" s="11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>-0.4524240846841507</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>-0.4048481693683015</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>-0.3572722540524522</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>-0.309696338736603</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>-0.2621204234207537</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>-0.2145445081049045</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>-0.1669685927890552</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>-0.1669685927890552</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>-0.1669685927890552</v>
       </c>
     </row>
     <row r="8">
@@ -3191,43 +3454,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="19">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="19">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="19">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3238,35 +3501,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
-        <v>-48.42987125285001</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>-92.99425039999998</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>-95.78407791199999</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>-98.65760024936</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>-101.6173282568408</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>-104.665848104546</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>-107.8058235476824</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>-111.0399982541129</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>-114.3711982017363</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>-117.8023341477884</v>
+      <c r="B9" s="18" t="n">
+        <v>-48.4434917285</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>-44.11829193003474</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>-43.4309879864308</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-41.40259350827562</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>-38.27404469873833</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>-34.2514302387272</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>-29.4968071901614</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>-24.13019151245495</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>-24.92671044973136</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>-25.51372821097464</v>
       </c>
     </row>
     <row r="10">
@@ -3317,40 +3580,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Levered FCF (mn)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>-48.42987125285001</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>-50.12491674669975</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>-51.87928883283423</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-53.69506394198343</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>-55.57439117995285</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>-57.51949487125119</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>-59.53267719174497</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>-61.61632089345604</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>-63.77289212472699</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>-66.00494334909244</v>
+      <c r="B12" s="20" t="n">
+        <v>-37.29796246477009</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>-38.74960149922767</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>-38.32513568214763</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-36.68561826947162</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>-34.04009499892048</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-30.57211406218097</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-26.42880673506881</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>-21.72088413627331</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>-22.54902893426172</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>-23.27801602881564</v>
       </c>
     </row>
     <row r="13">
@@ -3359,43 +3622,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="12">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3403,438 +3666,8 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UEC — 2-Stage Free Cash Flow to Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Levered beta (clamped 0.8–2.0)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity = Rf + β·ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>$B$5+$B$7*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Perpetual growth (g)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>454.015855</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stage 1 — 10-year cash-flow forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cash flow (mn)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PV (mn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>-48.42987125285001</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D15" s="22">
-        <f>1/(1+$B$8)^1</f>
-        <v/>
-      </c>
-      <c r="E15" s="12">
-        <f>B15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>-50.12491674669975</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>1/(1+$B$8)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="12">
-        <f>B16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>-51.87928883283423</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>1/(1+$B$8)^3</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
-        <f>B17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>-53.69506394198343</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>1/(1+$B$8)^4</f>
-        <v/>
-      </c>
-      <c r="E18" s="12">
-        <f>B18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>-55.57439117995285</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>1/(1+$B$8)^5</f>
-        <v/>
-      </c>
-      <c r="E19" s="12">
-        <f>B19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>-57.51949487125119</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D20" s="22">
-        <f>1/(1+$B$8)^6</f>
-        <v/>
-      </c>
-      <c r="E20" s="12">
-        <f>B20*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>-59.53267719174497</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D21" s="22">
-        <f>1/(1+$B$8)^7</f>
-        <v/>
-      </c>
-      <c r="E21" s="12">
-        <f>B21*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>-61.61632089345604</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D22" s="22">
-        <f>1/(1+$B$8)^8</f>
-        <v/>
-      </c>
-      <c r="E22" s="12">
-        <f>B22*D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>-63.77289212472699</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D23" s="22">
-        <f>1/(1+$B$8)^9</f>
-        <v/>
-      </c>
-      <c r="E23" s="12">
-        <f>B23*D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>-66.00494334909244</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D24" s="22">
-        <f>1/(1+$B$8)^10</f>
-        <v/>
-      </c>
-      <c r="E24" s="12">
-        <f>B24*D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>PV of next 10 years' cash flows</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2 — terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
-        </is>
-      </c>
-      <c r="B28" s="12">
-        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B29" s="12">
-        <f>$B$28/(1+$B$8)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Total equity value</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>$B$25+$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>9.930000305175781</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B34" s="13">
-        <f>B32/$B$33-1</f>
-        <v/>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3848,7 +3681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3874,7 +3707,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-08.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: Yahoo snapshot as of 2026-07-08, retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3734,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="18" t="n">
         <v>454.015855</v>
       </c>
     </row>
@@ -3911,8 +3744,8 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v/>
+      <c r="B7" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3921,7 +3754,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="18" t="n">
         <v>148.93</v>
       </c>
     </row>
@@ -3931,7 +3764,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3941,7 +3774,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="19">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -3959,7 +3792,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -3969,7 +3802,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -3979,7 +3812,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3989,7 +3822,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3999,8 +3832,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
-        <v>1</v>
+      <c r="B17" s="22" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="18">
@@ -4009,7 +3842,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -4019,7 +3852,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4036,7 +3869,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -4093,6 +3926,16 @@
           <t>FY2033E</t>
         </is>
       </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4100,29 +3943,35 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>0.2178571428571429</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0.1857142857142857</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0.1535714285714286</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0.1214285714285714</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>0.08928571428571427</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>0.05714285714285713</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>0.02499999999999999</v>
+      <c r="C26" s="11" t="n">
+        <v>0.1289463188433485</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.09951611862815915</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.07841845673028561</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.06329415127866128</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.0524519728182562</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.04467952772031308</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.03910768595242882</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.03511339325622756</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -4131,29 +3980,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>-1.098508311264719</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>-0.941578552512616</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>-0.7846487937605133</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>-0.6277190350084108</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>-0.4707892762563081</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>-0.3138595175042054</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>-0.1569297587521027</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>0</v>
+      <c r="B27" s="11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>-0.4524240846841507</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>-0.4048481693683015</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>-0.3572722540524522</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>-0.309696338736603</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>-0.2621204234207537</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>-0.2145445081049045</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>-0.1669685927890552</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>-0.1669685927890552</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>-0.1669685927890552</v>
       </c>
     </row>
     <row r="28">
@@ -4162,28 +4017,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="G28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="I28" s="11" t="n">
+        <v>0.04628903394213016</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.04628903394213016</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.04628903394213016</v>
       </c>
     </row>
@@ -4193,29 +4054,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.04714694156539385</v>
       </c>
-      <c r="C29" s="14" t="n">
-        <v>0.04714694156539385</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>0.04714694156539385</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>0.04714694156539385</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>0.04714694156539385</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>0.04714694156539385</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>0.04714694156539385</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>0.04714694156539385</v>
+      <c r="C29" s="11" t="n">
+        <v>0.04756594109549933</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.04798494062560481</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.04840394015571029</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.04882293968581577</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.04924193921592125</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.04966093874602674</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.05007993827613222</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.0504989378062377</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.05091793733634318</v>
       </c>
     </row>
     <row r="30">
@@ -4224,8 +4091,8 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>-0.1694960375211826</v>
+      <c r="B30" s="11" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4288,7 +4155,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -4299,7 +4166,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -4310,7 +4177,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4321,18 +4188,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -4348,7 +4215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4364,6 +4231,8 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4446,6 +4315,16 @@
           <t>FY2033E</t>
         </is>
       </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4453,48 +4332,56 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>23.161</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>164.389</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.224</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>66.837</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="19">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="19">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="19">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="19">
         <f>I5*(1+Assumptions!F$26)</f>
         <v/>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="19">
         <f>J5*(1+Assumptions!G$26)</f>
         <v/>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="19">
         <f>K5*(1+Assumptions!H$26)</f>
         <v/>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="19">
         <f>L5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="19">
+        <f>M5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="O5" s="19">
+        <f>N5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -4504,48 +4391,56 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <f>L5/K5-1</f>
         <v/>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>O5/N5-1</f>
         <v/>
       </c>
     </row>
@@ -4555,48 +4450,56 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>-18.949</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>-56.553</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>-73.42100000000001</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="19">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="19">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="19">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="19">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="19">
         <f>J5*Assumptions!F$27</f>
         <v/>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="19">
         <f>K5*Assumptions!G$27</f>
         <v/>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="19">
         <f>L5*Assumptions!H$27</f>
         <v/>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="19">
         <f>M5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>N5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="O7" s="19">
+        <f>O5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -4606,52 +4509,60 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <f>J7/J5</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <f>K7/K5</f>
         <v/>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <f>L7/L5</f>
         <v/>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>O7/O5</f>
         <v/>
       </c>
     </row>
@@ -4661,48 +4572,56 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>4.486</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="19">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="19">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="19">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="19">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="19">
         <f>J5*Assumptions!F$28</f>
         <v/>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="19">
         <f>K5*Assumptions!G$28</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="19">
         <f>L5*Assumptions!H$28</f>
         <v/>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="19">
         <f>M5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>N5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f>O5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -4712,52 +4631,60 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="27">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="19">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="19">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="19">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="19">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="19">
         <f>J7+J9</f>
         <v/>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="19">
         <f>K7+K9</f>
         <v/>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="19">
         <f>L7+L9</f>
         <v/>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="19">
         <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>N7+N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="19">
+        <f>O7+O9</f>
         <v/>
       </c>
     </row>
@@ -4767,52 +4694,60 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="28">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="23">
         <f>J7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="23">
         <f>K7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="23">
         <f>L7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="23">
         <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>O7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -4822,48 +4757,56 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>1.21</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>0.656</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>3.428</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>5.695</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="19">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="19">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="19">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="19">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="19">
         <f>J5*Assumptions!F$29</f>
         <v/>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="19">
         <f>K5*Assumptions!G$29</f>
         <v/>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="19">
         <f>L5*Assumptions!H$29</f>
         <v/>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="19">
         <f>M5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>N5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f>O5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -4873,103 +4816,119 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>35.495</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>-57.032</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>59.318</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>4.319</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="19">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="19">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="19">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="19">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="19">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="19">
         <f>(K5-J5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="19">
         <f>(L5-K5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="19">
         <f>(M5-L5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="N13" s="19">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>(O5-N5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="29">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="30">
         <f>J11+J9-J12-J13</f>
         <v/>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="30">
         <f>K11+K9-K12-K13</f>
         <v/>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="30">
         <f>L11+L9-L12-L13</f>
         <v/>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="30">
         <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="30">
+        <f>O11+O9-O12-O13</f>
         <v/>
       </c>
     </row>
@@ -4984,7 +4943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4997,6 +4956,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5059,6 +5020,16 @@
           <t>FY2033E</t>
         </is>
       </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5066,36 +5037,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <f>Model!J14</f>
         <v/>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="23">
         <f>Model!K14</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="23">
         <f>Model!L14</f>
         <v/>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="23">
         <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!N14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!O14</f>
         <v/>
       </c>
     </row>
@@ -5105,29 +5084,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="31" t="n">
         <v>5.5</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="31" t="n">
         <v>6.5</v>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I6" s="31" t="n">
         <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -5136,36 +5121,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
         <v/>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="32">
         <f>1/(1+WACC!$B$10)^G6</f>
         <v/>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="32">
         <f>1/(1+WACC!$B$10)^H6</f>
         <v/>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="32">
         <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -5175,36 +5168,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="19">
         <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -5214,8 +5215,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="12">
-        <f>SUM(B8:I8)</f>
+      <c r="B10" s="19">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -5225,8 +5226,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>Model!M11</f>
+      <c r="B11" s="23">
+        <f>Model!O11</f>
         <v/>
       </c>
     </row>
@@ -5236,8 +5237,8 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
-        <v/>
+      <c r="B12" s="18" t="n">
+        <v>834.97</v>
       </c>
     </row>
     <row r="13">
@@ -5246,8 +5247,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="27">
-        <f>$B$12*Model!M5/Model!E5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!O5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -5257,7 +5258,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5268,7 +5269,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -5279,7 +5280,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="19">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5290,8 +5291,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="12">
-        <f>$B$16/(1+WACC!$B$10)^(8-0.5)</f>
+      <c r="B17" s="19">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -5301,18 +5302,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -5323,7 +5324,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -5334,40 +5335,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -5409,149 +5410,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.074</v>
+      <c r="A5" s="15" t="n">
+        <v>0.0786</v>
       </c>
       <c r="B5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$5)^DCF!$B$6:$I$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$5)^DCF!$B$6:$I$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$5)^DCF!$B$6:$I$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$5)^DCF!$B$6:$I$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$5)^DCF!$B$6:$I$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.08149999999999999</v>
+      <c r="A6" s="15" t="n">
+        <v>0.08610000000000001</v>
       </c>
       <c r="B6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$6)^DCF!$B$6:$I$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$6)^DCF!$B$6:$I$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$6)^DCF!$B$6:$I$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$6)^DCF!$B$6:$I$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$6)^DCF!$B$6:$I$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.089</v>
+      <c r="A7" s="15" t="n">
+        <v>0.0936</v>
       </c>
       <c r="B7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$7)^DCF!$B$6:$I$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$7)^DCF!$B$6:$I$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$7)^DCF!$B$6:$I$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$7)^DCF!$B$6:$I$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$7)^DCF!$B$6:$I$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.0965</v>
+      <c r="A8" s="15" t="n">
+        <v>0.1011</v>
       </c>
       <c r="B8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$8)^DCF!$B$6:$I$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$8)^DCF!$B$6:$I$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$8)^DCF!$B$6:$I$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$8)^DCF!$B$6:$I$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$8)^DCF!$B$6:$I$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.104</v>
+      <c r="A9" s="15" t="n">
+        <v>0.1086</v>
       </c>
       <c r="B9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$9)^DCF!$B$6:$I$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$9)^DCF!$B$6:$I$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$9)^DCF!$B$6:$I$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$9)^DCF!$B$6:$I$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$I$5,1/(1+$A$9)^DCF!$B$6:$I$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(8-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -5587,7 +5588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -5629,16 +5630,16 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>4.50177</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-2.00025</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>2.851399854036</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>-0.5022081826729999</v>
       </c>
     </row>
@@ -5648,17 +5649,17 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>1.46957e-07</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>3.0729e-08</v>
+      <c r="C6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>1.46957e-13</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>3.0729e-14</v>
       </c>
     </row>
     <row r="7">
@@ -5667,16 +5668,16 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-13.292</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>9.9</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>-50.648</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>-68.16</v>
       </c>
     </row>
@@ -5686,16 +5687,16 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>21.437</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>-9.525</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>19.403</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>-16.343</v>
       </c>
     </row>
@@ -5705,16 +5706,16 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>21.437</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-9.525</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>19.403</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>-16.343</v>
       </c>
     </row>
@@ -5724,16 +5725,16 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -5743,16 +5744,16 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>4.486</v>
       </c>
     </row>
@@ -5762,16 +5763,16 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>15.868</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>114.719</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>0.187</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>42.348</v>
       </c>
     </row>
@@ -5781,16 +5782,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>8.145</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.375</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>-31.245</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>-84.503</v>
       </c>
     </row>
@@ -5800,16 +5801,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>6.766</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>-1.632</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>-33.428</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>-88.989</v>
       </c>
     </row>
@@ -5819,16 +5820,16 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-1.421</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>-0.455</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>1.802</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>2.576</v>
       </c>
     </row>
@@ -5838,16 +5839,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>1.519</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>0.805</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.827</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>1.446</v>
       </c>
     </row>
@@ -5857,16 +5858,16 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>0.098</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>0.35</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>2.629</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -5876,16 +5877,16 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-11.68323</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>4.21775</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>-45.772600145964</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>-71.815208182673</v>
       </c>
     </row>
@@ -5895,16 +5896,16 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -5914,16 +5915,16 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>42.11</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>155.339</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>56.777</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>140.258</v>
       </c>
     </row>
@@ -5933,16 +5934,16 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-22.71</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>8.867000000000001</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>-56.402</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>-73.321</v>
       </c>
     </row>
@@ -5952,16 +5953,16 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>280.102073</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>364.789621</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>397.30978</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>427.680193</v>
       </c>
     </row>
@@ -5971,16 +5972,16 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>271.019472</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>364.789621</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>397.30978</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>427.680193</v>
       </c>
     </row>
@@ -5990,17 +5991,17 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>-2e-07</v>
+      <c r="C24" s="25" t="n">
+        <v>2e-14</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>-1e-14</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>-7e-14</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>-2e-13</v>
       </c>
     </row>
     <row r="25">
@@ -6009,17 +6010,17 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>-2e-07</v>
+      <c r="C25" s="25" t="n">
+        <v>2e-14</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>-1e-14</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>-7e-14</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>-2e-13</v>
       </c>
     </row>
     <row r="26">
@@ -6028,16 +6029,16 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -6047,16 +6048,16 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -6066,16 +6067,16 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -6085,16 +6086,16 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -6104,16 +6105,16 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>5.252</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>-3.307</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>-29.221</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>-87.65600000000001</v>
       </c>
     </row>
@@ -6123,16 +6124,16 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>0.87</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>-5.034</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>-2.779</v>
       </c>
     </row>
@@ -6142,16 +6143,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>5.247</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-2.437</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>-34.255</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>-90.435</v>
       </c>
     </row>
@@ -6161,16 +6162,16 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>25.617</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>-11.032</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>20.496</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>-19.59</v>
       </c>
     </row>
@@ -6180,16 +6181,16 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>0.054</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>-0.513</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>0.076</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>0.105</v>
       </c>
     </row>
@@ -6199,16 +6200,16 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>23.105</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-0.748</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>-0.027</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>-0.098</v>
       </c>
     </row>
@@ -6218,16 +6219,16 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>6.427</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>0.02</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-0.027</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>-0.098</v>
       </c>
     </row>
@@ -6237,13 +6238,13 @@
           <t>Other Special Charges</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="25" t="n">
         <v>-0.286</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>-1.78</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>-0.428</v>
       </c>
     </row>
@@ -6253,16 +6254,16 @@
           <t>Write Off</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>-18.342</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6272,16 +6273,16 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>0.112</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6291,16 +6292,16 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>3.444</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>1.084</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6310,16 +6311,16 @@
           <t>Earnings From Equity Interest</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>4.126</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>-0.994</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>1.017</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>-3.352</v>
       </c>
     </row>
@@ -6329,16 +6330,16 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>-1.668</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>-8.776999999999999</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>19.43</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>-16.245</v>
       </c>
     </row>
@@ -6348,16 +6349,16 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-1.421</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>-0.455</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>1.802</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>2.576</v>
       </c>
     </row>
@@ -6367,16 +6368,16 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>1.519</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>0.805</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>0.827</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>1.446</v>
       </c>
     </row>
@@ -6386,16 +6387,16 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>0.098</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>0.35</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>2.629</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -6405,16 +6406,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>-18.949</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>-56.553</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>-73.42100000000001</v>
       </c>
     </row>
@@ -6424,16 +6425,16 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>26.242</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>40.62</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>56.59</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>97.898</v>
       </c>
     </row>
@@ -6443,16 +6444,16 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>10.154</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>18.62</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>32.383</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>66.06399999999999</v>
       </c>
     </row>
@@ -6462,16 +6463,16 @@
           <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>4.474</v>
       </c>
     </row>
@@ -6481,16 +6482,16 @@
           <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>1.379</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>2.007</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>2.183</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>4.474</v>
       </c>
     </row>
@@ -6500,16 +6501,16 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>14.709</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>19.993</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>22.024</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>27.36</v>
       </c>
     </row>
@@ -6519,16 +6520,16 @@
           <t>General And Administrative Expense</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>14.709</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>19.993</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>22.024</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>27.36</v>
       </c>
     </row>
@@ -6538,16 +6539,16 @@
           <t>Other Gand A</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>5.888</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>9.41</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>9.147</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>11.385</v>
       </c>
     </row>
@@ -6557,16 +6558,16 @@
           <t>Salaries And Wages</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>8.821</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>10.583</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>12.877</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>15.975</v>
       </c>
     </row>
@@ -6576,16 +6577,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>7.293</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>49.67</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>0.037</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>24.477</v>
       </c>
     </row>
@@ -6595,16 +6596,16 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>15.868</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>114.719</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>0.187</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>42.36</v>
       </c>
     </row>
@@ -6614,16 +6615,16 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>23.161</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>164.389</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>0.224</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>66.837</v>
       </c>
     </row>
@@ -6633,16 +6634,16 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>23.161</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>164.389</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>0.224</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>66.837</v>
       </c>
     </row>

--- a/docs/reports/UEC.xlsx
+++ b/docs/reports/UEC.xlsx
@@ -3224,7 +3224,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Target 3.68 fell outside 0.4x–2.5x the price and was limited to the band edge.</t>
+          <t>Target $3.68 fell outside 0.4x–2.5x the price and was limited to the band edge.</t>
         </is>
       </c>
     </row>

--- a/docs/reports/UEC.xlsx
+++ b/docs/reports/UEC.xlsx
@@ -3336,31 +3336,31 @@
         <v>83.54625</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>94.31923139066612</v>
+        <v>96.48740827932684</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>103.7055152106564</v>
+        <v>109.1581353510335</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>111.8379416678953</v>
+        <v>121.0969039785811</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>118.9166292665171</v>
+        <v>131.8967415632188</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>125.1540410724432</v>
+        <v>141.2516400852026</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>130.7458645198486</v>
+        <v>148.9964341627106</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>135.8590327290696</v>
+        <v>155.1406398745866</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>140.6295043726961</v>
+        <v>159.9097780633238</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>144.1452419820135</v>
+        <v>163.9075225149069</v>
       </c>
     </row>
     <row r="6">
@@ -3505,31 +3505,31 @@
         <v>-48.4434917285</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>-44.11829193003474</v>
+        <v>-45.09922737432039</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>-43.4309879864308</v>
+        <v>-45.6384712685232</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-41.40259350827562</v>
+        <v>-44.71056384320104</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>-38.27404469873833</v>
+        <v>-42.29393795341679</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-34.2514302387272</v>
+        <v>-38.47093970800922</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>-29.4968071901614</v>
+        <v>-33.41236667682352</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>-24.13019151245495</v>
+        <v>-27.34961432425331</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>-24.92671044973136</v>
+        <v>-28.14591061644332</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>-25.51372821097464</v>
+        <v>-28.8134083818544</v>
       </c>
     </row>
     <row r="10">
@@ -3589,31 +3589,31 @@
         <v>-37.29796246477009</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>-38.74960149922767</v>
+        <v>-39.4183942707976</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>-38.32513568214763</v>
+        <v>-39.99267344579766</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>-36.68561826947162</v>
+        <v>-39.30173919079579</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>-34.04009499892048</v>
+        <v>-37.3187743106318</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>-30.57211406218097</v>
+        <v>-34.10545859794915</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>-26.42880673506881</v>
+        <v>-29.79905239350708</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>-21.72088413627331</v>
+        <v>-24.5883556447208</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>-22.54902893426172</v>
+        <v>-25.52761052850262</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>-23.27801602881564</v>
+        <v>-26.29100518581695</v>
       </c>
     </row>
     <row r="13">
@@ -3947,28 +3947,28 @@
         <v>0.25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.1289463188433485</v>
+        <v>0.1548981346179732</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.09951611862815915</v>
+        <v>0.1313200063890771</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.07841845673028561</v>
+        <v>0.1093713133625317</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.06329415127866128</v>
+        <v>0.08918343268749396</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.0524519728182562</v>
+        <v>0.07092592592592592</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.04467952772031308</v>
+        <v>0.05482976390813067</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.03910768595242882</v>
+        <v>0.04123726682724665</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.03511339325622756</v>
+        <v>0.03074074074074075</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
